--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0001T0006Z000C1N37_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0001T0006Z000C1N37_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>33.73122086982642</v>
+        <v>5.481323391346794</v>
       </c>
       <c r="D2" t="n">
-        <v>33.60676019955837</v>
+        <v>5.461098532428236</v>
       </c>
       <c r="E2" t="n">
-        <v>16.44000165161571</v>
+        <v>2.671500268387554</v>
       </c>
       <c r="F2" t="n">
-        <v>15.03690628198585</v>
+        <v>2.443497270822701</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>52.80057952538877</v>
+        <v>8.580094172875675</v>
       </c>
       <c r="D3" t="n">
-        <v>52.9454293313968</v>
+        <v>8.60363226635198</v>
       </c>
       <c r="E3" t="n">
-        <v>16.44000165161571</v>
+        <v>2.671500268387554</v>
       </c>
       <c r="F3" t="n">
-        <v>15.03690628198585</v>
+        <v>2.443497270822701</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>45.91341038256977</v>
+        <v>7.460929187167588</v>
       </c>
       <c r="D4" t="n">
-        <v>46.08420279946916</v>
+        <v>7.488682954913739</v>
       </c>
       <c r="E4" t="n">
-        <v>16.44000165161571</v>
+        <v>2.671500268387554</v>
       </c>
       <c r="F4" t="n">
-        <v>15.03690628198585</v>
+        <v>2.443497270822701</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>67.54407039065579</v>
+        <v>10.97591143848157</v>
       </c>
       <c r="D5" t="n">
-        <v>54.69232121605372</v>
+        <v>8.887502197608731</v>
       </c>
       <c r="E5" t="n">
-        <v>16.44000165161571</v>
+        <v>2.671500268387554</v>
       </c>
       <c r="F5" t="n">
-        <v>15.03690628198585</v>
+        <v>2.443497270822701</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>53.16567941903414</v>
+        <v>8.639422905593049</v>
       </c>
       <c r="D6" t="n">
-        <v>53.36210614435106</v>
+        <v>8.671342248457048</v>
       </c>
       <c r="E6" t="n">
-        <v>16.44000165161571</v>
+        <v>2.671500268387554</v>
       </c>
       <c r="F6" t="n">
-        <v>15.03690628198585</v>
+        <v>2.443497270822701</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>70.04422363807089</v>
+        <v>11.38218634118652</v>
       </c>
       <c r="D7" t="n">
-        <v>44.28194374352981</v>
+        <v>7.195815858323594</v>
       </c>
       <c r="E7" t="n">
-        <v>16.44000165161571</v>
+        <v>2.671500268387554</v>
       </c>
       <c r="F7" t="n">
-        <v>15.03690628198585</v>
+        <v>2.443497270822701</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>22.30315141562338</v>
+        <v>3.624262105038798</v>
       </c>
       <c r="D8" t="n">
-        <v>22.52484252395661</v>
+        <v>3.66028691014295</v>
       </c>
       <c r="E8" t="n">
-        <v>16.44000165161571</v>
+        <v>2.671500268387554</v>
       </c>
       <c r="F8" t="n">
-        <v>15.03690628198585</v>
+        <v>2.443497270822701</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>65.57397489939694</v>
+        <v>10.655770921152</v>
       </c>
       <c r="D9" t="n">
-        <v>33.18508701209024</v>
+        <v>5.392576639464663</v>
       </c>
       <c r="E9" t="n">
-        <v>16.44000165161571</v>
+        <v>2.671500268387554</v>
       </c>
       <c r="F9" t="n">
-        <v>15.03690628198585</v>
+        <v>2.443497270822701</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>44.35571095473497</v>
+        <v>7.207803030144434</v>
       </c>
       <c r="D10" t="n">
-        <v>28.90069203323685</v>
+        <v>4.696362455400989</v>
       </c>
       <c r="E10" t="n">
-        <v>16.44000165161571</v>
+        <v>2.671500268387554</v>
       </c>
       <c r="F10" t="n">
-        <v>15.03690628198585</v>
+        <v>2.443497270822701</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>61.38043405311816</v>
+        <v>9.974320533631701</v>
       </c>
       <c r="D11" t="n">
-        <v>23.34664510232222</v>
+        <v>3.79382982912736</v>
       </c>
       <c r="E11" t="n">
-        <v>16.44000165161571</v>
+        <v>2.671500268387554</v>
       </c>
       <c r="F11" t="n">
-        <v>15.03690628198585</v>
+        <v>2.443497270822701</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>47.55043431712021</v>
+        <v>7.726945576532035</v>
       </c>
       <c r="D12" t="n">
-        <v>14.48162115249024</v>
+        <v>2.353263437279664</v>
       </c>
       <c r="E12" t="n">
-        <v>16.44000165161571</v>
+        <v>2.671500268387554</v>
       </c>
       <c r="F12" t="n">
-        <v>15.03690628198585</v>
+        <v>2.443497270822701</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>32.31472097663003</v>
+        <v>5.251142158702381</v>
       </c>
       <c r="D13" t="n">
-        <v>31.89293156118715</v>
+        <v>5.182601378692912</v>
       </c>
       <c r="E13" t="n">
-        <v>16.44000165161571</v>
+        <v>2.671500268387554</v>
       </c>
       <c r="F13" t="n">
-        <v>15.03690628198585</v>
+        <v>2.443497270822701</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>50.41736171654687</v>
+        <v>8.192821278938867</v>
       </c>
       <c r="D14" t="n">
-        <v>5.590169943749475</v>
+        <v>0.9084026158592896</v>
       </c>
       <c r="E14" t="n">
-        <v>16.44000165161571</v>
+        <v>2.671500268387554</v>
       </c>
       <c r="F14" t="n">
-        <v>15.03690628198585</v>
+        <v>2.443497270822701</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>25.51316976480787</v>
+        <v>4.145890086781279</v>
       </c>
       <c r="D15" t="n">
-        <v>25.3416572941648</v>
+        <v>4.118019310301781</v>
       </c>
       <c r="E15" t="n">
-        <v>16.44000165161571</v>
+        <v>2.671500268387554</v>
       </c>
       <c r="F15" t="n">
-        <v>15.03690628198585</v>
+        <v>2.443497270822701</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>10.12670085558071</v>
+        <v>1.645588889031866</v>
       </c>
       <c r="D16" t="n">
-        <v>10.08547540140767</v>
+        <v>1.638889752728746</v>
       </c>
       <c r="E16" t="n">
-        <v>16.44000165161571</v>
+        <v>2.671500268387554</v>
       </c>
       <c r="F16" t="n">
-        <v>15.03690628198585</v>
+        <v>2.443497270822701</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>27.65996281549905</v>
+        <v>4.494743957518596</v>
       </c>
       <c r="D17" t="n">
-        <v>27.72815178922859</v>
+        <v>4.505824665749647</v>
       </c>
       <c r="E17" t="n">
-        <v>16.44000165161571</v>
+        <v>2.671500268387554</v>
       </c>
       <c r="F17" t="n">
-        <v>15.03690628198585</v>
+        <v>2.443497270822701</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>37.47472423339445</v>
+        <v>6.089642687926598</v>
       </c>
       <c r="D18" t="n">
-        <v>29.7405447159261</v>
+        <v>4.832838516337992</v>
       </c>
       <c r="E18" t="n">
-        <v>16.44000165161571</v>
+        <v>2.671500268387554</v>
       </c>
       <c r="F18" t="n">
-        <v>15.03690628198585</v>
+        <v>2.443497270822701</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>55.91550278096997</v>
+        <v>9.086269201907619</v>
       </c>
       <c r="D19" t="n">
-        <v>56.46842460090421</v>
+        <v>9.176118997646935</v>
       </c>
       <c r="E19" t="n">
-        <v>16.44000165161571</v>
+        <v>2.671500268387554</v>
       </c>
       <c r="F19" t="n">
-        <v>15.03690628198585</v>
+        <v>2.443497270822701</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
